--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008439271833561955</v>
       </c>
       <c r="C2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>18862652</v>
+        <v>4481982</v>
       </c>
       <c r="L2" t="n">
-        <v>11491738</v>
+        <v>2522412</v>
       </c>
       <c r="M2" t="n">
-        <v>2997104</v>
+        <v>614518</v>
       </c>
       <c r="N2" t="n">
-        <v>175045</v>
+        <v>20694</v>
       </c>
       <c r="O2" t="n">
-        <v>1753062</v>
+        <v>372200</v>
       </c>
       <c r="P2" t="n">
-        <v>684917</v>
+        <v>148710</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999498128890991</v>
+        <v>0.9999285936355591</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9382727146148682</v>
+        <v>0.881390392780304</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8631651401519775</v>
+        <v>0.7638654112815857</v>
       </c>
       <c r="T2" t="n">
-        <v>0.832489550113678</v>
+        <v>0.6918346881866455</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6369233131408691</v>
+        <v>0.3181538581848145</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8668020367622375</v>
+        <v>0.7483964562416077</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9123784303665161</v>
+        <v>0.8342402577400208</v>
       </c>
       <c r="X2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="AG2" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AH2" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AI2" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566228985786438</v>
+        <v>0.956451416015625</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112591743469238</v>
+        <v>0.9113048315048218</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.858102023601532</v>
+        <v>0.8578755855560303</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624639630317688</v>
+        <v>0.6619618535041809</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020282030105591</v>
+        <v>0.9019733667373657</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002023734838753813</v>
       </c>
       <c r="C3" t="n">
-        <v>756</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>18862652</v>
+        <v>4481982</v>
       </c>
       <c r="E3" t="n">
-        <v>1246362</v>
+        <v>532834</v>
       </c>
       <c r="F3" t="n">
-        <v>12642</v>
+        <v>7036</v>
       </c>
       <c r="G3" t="n">
-        <v>1914</v>
+        <v>827</v>
       </c>
       <c r="H3" t="n">
-        <v>606</v>
+        <v>337</v>
       </c>
       <c r="I3" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>40065220</v>
+        <v>10016171</v>
       </c>
       <c r="K3" t="n">
-        <v>43952493</v>
+        <v>10703226</v>
       </c>
       <c r="L3" t="n">
-        <v>50448902</v>
+        <v>12280957</v>
       </c>
       <c r="M3" t="n">
-        <v>60987457</v>
+        <v>15123283</v>
       </c>
       <c r="N3" t="n">
-        <v>64862227</v>
+        <v>16196059</v>
       </c>
       <c r="O3" t="n">
-        <v>63012700</v>
+        <v>15695092</v>
       </c>
       <c r="P3" t="n">
-        <v>64479431</v>
+        <v>16106706</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9372761845588684</v>
+        <v>0.892251193523407</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8807448744773865</v>
+        <v>0.7716424465179443</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8039707541465759</v>
+        <v>0.6589362621307373</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4911627471446991</v>
+        <v>0.2320189327001572</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8608996272087097</v>
+        <v>0.7306950688362122</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8858304023742676</v>
+        <v>0.769139289855957</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="Z3" t="n">
-        <v>791602</v>
+        <v>198076</v>
       </c>
       <c r="AA3" t="n">
-        <v>34131</v>
+        <v>8559</v>
       </c>
       <c r="AB3" t="n">
-        <v>27146</v>
+        <v>6810</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40066488</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>44319573</v>
+        <v>11087378</v>
       </c>
       <c r="AG3" t="n">
-        <v>51114353</v>
+        <v>12771195</v>
       </c>
       <c r="AH3" t="n">
-        <v>61061800</v>
+        <v>15264532</v>
       </c>
       <c r="AI3" t="n">
-        <v>64841808</v>
+        <v>16210280</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63082667</v>
+        <v>15770309</v>
       </c>
       <c r="AK3" t="n">
-        <v>64492192</v>
+        <v>16123000</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576059579849243</v>
+        <v>0.9574934840202332</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100238084793091</v>
+        <v>0.909995973110199</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576881885528564</v>
+        <v>0.857442319393158</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66196209192276</v>
+        <v>0.6615017056465149</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016556143760681</v>
+        <v>0.9016192555427551</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03193050064849949</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1170623</v>
+        <v>570680</v>
       </c>
       <c r="E4" t="n">
-        <v>11491738</v>
+        <v>2522412</v>
       </c>
       <c r="F4" t="n">
-        <v>358886</v>
+        <v>160476</v>
       </c>
       <c r="G4" t="n">
-        <v>8499</v>
+        <v>4304</v>
       </c>
       <c r="H4" t="n">
-        <v>16917</v>
+        <v>10312</v>
       </c>
       <c r="I4" t="n">
-        <v>1080</v>
+        <v>699</v>
       </c>
       <c r="J4" t="n">
-        <v>1268</v>
+        <v>451</v>
       </c>
       <c r="K4" t="n">
-        <v>1240940</v>
+        <v>603145</v>
       </c>
       <c r="L4" t="n">
-        <v>1821749</v>
+        <v>779756</v>
       </c>
       <c r="M4" t="n">
-        <v>603066</v>
+        <v>273726</v>
       </c>
       <c r="N4" t="n">
-        <v>99784</v>
+        <v>44350</v>
       </c>
       <c r="O4" t="n">
-        <v>269386</v>
+        <v>125130</v>
       </c>
       <c r="P4" t="n">
-        <v>65777</v>
+        <v>29548</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999749064445496</v>
+        <v>0.9999642968177795</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9377742409706116</v>
+        <v>0.8867875933647156</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8718663454055786</v>
+        <v>0.7677342295646667</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8179816603660583</v>
+        <v>0.6749848127365112</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5546261072158813</v>
+        <v>0.2683437466621399</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8638406991958618</v>
+        <v>0.739439845085144</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8989084959030151</v>
+        <v>0.8003681898117065</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>815845</v>
+        <v>204447</v>
       </c>
       <c r="Z4" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AA4" t="n">
-        <v>331353</v>
+        <v>83051</v>
       </c>
       <c r="AB4" t="n">
-        <v>21937</v>
+        <v>5499</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>873860</v>
+        <v>218993</v>
       </c>
       <c r="AG4" t="n">
-        <v>1156298</v>
+        <v>289518</v>
       </c>
       <c r="AH4" t="n">
-        <v>528723</v>
+        <v>132477</v>
       </c>
       <c r="AI4" t="n">
-        <v>120203</v>
+        <v>30129</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199419</v>
+        <v>49913</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571141600608826</v>
+        <v>0.9569721221923828</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910641074180603</v>
+        <v>0.9106499552726746</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578950166702271</v>
+        <v>0.857658863067627</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622129082679749</v>
+        <v>0.6617317199707031</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018418788909912</v>
+        <v>0.9017962217330933</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>349</v>
+        <v>178</v>
       </c>
       <c r="D5" t="n">
-        <v>41807</v>
+        <v>19684</v>
       </c>
       <c r="E5" t="n">
-        <v>500050</v>
+        <v>215833</v>
       </c>
       <c r="F5" t="n">
-        <v>2997104</v>
+        <v>614518</v>
       </c>
       <c r="G5" t="n">
-        <v>40775</v>
+        <v>16148</v>
       </c>
       <c r="H5" t="n">
-        <v>140700</v>
+        <v>61932</v>
       </c>
       <c r="I5" t="n">
-        <v>7092</v>
+        <v>4298</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1262315</v>
+        <v>541247</v>
       </c>
       <c r="L5" t="n">
-        <v>1556011</v>
+        <v>746475</v>
       </c>
       <c r="M5" t="n">
-        <v>730773</v>
+        <v>318073</v>
       </c>
       <c r="N5" t="n">
-        <v>181344</v>
+        <v>68497</v>
       </c>
       <c r="O5" t="n">
-        <v>283252</v>
+        <v>137178</v>
       </c>
       <c r="P5" t="n">
-        <v>88275</v>
+        <v>44636</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999805688858032</v>
+        <v>0.999972403049469</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9616761207580566</v>
+        <v>0.9299191832542419</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9482877850532532</v>
+        <v>0.9065359234809875</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9795794486999512</v>
+        <v>0.9637591242790222</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9956960082054138</v>
+        <v>0.9930894374847412</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9915392994880676</v>
+        <v>0.9839366674423218</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9976415038108826</v>
+        <v>0.9954571127891541</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32012</v>
+        <v>8028</v>
       </c>
       <c r="Z5" t="n">
-        <v>339750</v>
+        <v>85185</v>
       </c>
       <c r="AA5" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AB5" t="n">
-        <v>39755</v>
+        <v>9960</v>
       </c>
       <c r="AC5" t="n">
-        <v>116472</v>
+        <v>29142</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>853179</v>
+        <v>213520</v>
       </c>
       <c r="AG5" t="n">
-        <v>1173987</v>
+        <v>294213</v>
       </c>
       <c r="AH5" t="n">
-        <v>530521</v>
+        <v>132948</v>
       </c>
       <c r="AI5" t="n">
-        <v>120473</v>
+        <v>30191</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200260</v>
+        <v>50113</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735596776008606</v>
+        <v>0.9735135436058044</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643242359161377</v>
+        <v>0.9642531871795654</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837833642959595</v>
+        <v>0.9837457537651062</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963153600692749</v>
+        <v>0.9963061213493347</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938810467720032</v>
+        <v>0.9938745498657227</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998375415802002</v>
+        <v>0.9983739256858826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>28348</v>
+        <v>12712</v>
       </c>
       <c r="E6" t="n">
-        <v>56031</v>
+        <v>17904</v>
       </c>
       <c r="F6" t="n">
-        <v>64828</v>
+        <v>24582</v>
       </c>
       <c r="G6" t="n">
-        <v>175045</v>
+        <v>20694</v>
       </c>
       <c r="H6" t="n">
-        <v>30059</v>
+        <v>12369</v>
       </c>
       <c r="I6" t="n">
-        <v>2008</v>
+        <v>905</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25780</v>
+        <v>6462</v>
       </c>
       <c r="Z6" t="n">
-        <v>21382</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>43482</v>
+        <v>10898</v>
       </c>
       <c r="AB6" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AC6" t="n">
-        <v>27905</v>
+        <v>6984</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="E7" t="n">
-        <v>18418</v>
+        <v>12623</v>
       </c>
       <c r="F7" t="n">
-        <v>162473</v>
+        <v>78956</v>
       </c>
       <c r="G7" t="n">
-        <v>46676</v>
+        <v>21908</v>
       </c>
       <c r="H7" t="n">
-        <v>1753062</v>
+        <v>372200</v>
       </c>
       <c r="I7" t="n">
-        <v>55562</v>
+        <v>23633</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3240</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118437</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30304</v>
+        <v>7594</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E8" t="n">
-        <v>888</v>
+        <v>562</v>
       </c>
       <c r="F8" t="n">
-        <v>4237</v>
+        <v>2676</v>
       </c>
       <c r="G8" t="n">
-        <v>1920</v>
+        <v>1163</v>
       </c>
       <c r="H8" t="n">
-        <v>81104</v>
+        <v>40180</v>
       </c>
       <c r="I8" t="n">
-        <v>684917</v>
+        <v>148710</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
